--- a/gcexcel/demo_tpl.xlsx
+++ b/gcexcel/demo_tpl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuyujie/Project/opensource/jvmti-tools/gcexcel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\open-source\jtools\gcexcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C40A77-19DE-CA48-9AB0-70F70E60F212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2772D661-C078-4158-B09B-5CB7545A0748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5600" yWindow="2860" windowWidth="14380" windowHeight="9580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="1158" windowWidth="17280" windowHeight="10410" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>{{a}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -31,6 +31,18 @@
   </si>
   <si>
     <t>{{c}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{ds.a}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{ds.b}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{ds.c}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -38,7 +50,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,7 +74,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -70,12 +82,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -94,9 +122,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -134,7 +162,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -240,7 +268,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -382,7 +410,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -390,25 +418,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="8.84765625" defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18.6484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
